--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\arrowNew\AAAGameData\Configs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\Configs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="16575"/>
+    <workbookView windowWidth="27000" windowHeight="17175"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -258,42 +258,6 @@
     <t>Step2距目标最小保留缺口（占Step2_Mon比例，实际钳制在0.001~0.01）</t>
   </si>
   <si>
-    <t>ScratchCardCondition</t>
-  </si>
-  <si>
-    <t>刮卡奖励条件（每累计消除n次）</t>
-  </si>
-  <si>
-    <t>ScratchCardWinRate</t>
-  </si>
-  <si>
-    <t>刮刮卡中奖概率（0~100，百分比）</t>
-  </si>
-  <si>
-    <t>ScratchCardMatchCountWeights</t>
-  </si>
-  <si>
-    <t>刮刮卡中奖个数权重（1~3个，对应权重）</t>
-  </si>
-  <si>
-    <t>10,10,10</t>
-  </si>
-  <si>
-    <t>ScratchCardAutoPopup</t>
-  </si>
-  <si>
-    <t>刮卡满足条件后是否自动弹出（0否1是）</t>
-  </si>
-  <si>
-    <t>ScratchCardProbability</t>
-  </si>
-  <si>
-    <t>刮刮卡中奖概率（小奖，中奖，大奖）</t>
-  </si>
-  <si>
-    <t>70,25,5</t>
-  </si>
-  <si>
     <t>EliminationRewardCount</t>
   </si>
   <si>
@@ -310,12 +274,6 @@
   </si>
   <si>
     <t>胜利奖励倍数</t>
-  </si>
-  <si>
-    <t>ScratchRewardRate</t>
-  </si>
-  <si>
-    <t>刮卡奖励倍数</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1687,7 +1645,7 @@
         <v>74</v>
       </c>
       <c r="D36" s="1">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -1698,7 +1656,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -1708,73 +1666,7 @@
       <c r="C38" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="D38" s="1">
         <v>10</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -180,12 +180,6 @@
     <t>广告类型气泡出现权重（点击气泡直接播放广告领取奖励，百分比）</t>
   </si>
   <si>
-    <t>MakeupAmount</t>
-  </si>
-  <si>
-    <t>提现数值</t>
-  </si>
-  <si>
     <t>DefaultProp</t>
   </si>
   <si>
@@ -198,15 +192,6 @@
     <t>引导开关（0关1开）</t>
   </si>
   <si>
-    <t>SavingPotRewards</t>
-  </si>
-  <si>
-    <t>存钱罐任务美元奖励</t>
-  </si>
-  <si>
-    <t>10,20,30,40,50</t>
-  </si>
-  <si>
     <t>GameTimeOut</t>
   </si>
   <si>
@@ -238,24 +223,6 @@
   </si>
   <si>
     <t>100,230</t>
-  </si>
-  <si>
-    <t>Step2ExpectedAdCount</t>
-  </si>
-  <si>
-    <t>Step2预计广告次数（渐近趋近目标）</t>
-  </si>
-  <si>
-    <t>Step2AsymptoteRatio</t>
-  </si>
-  <si>
-    <t>Step2预计广告后趋近目标比例（0-1）</t>
-  </si>
-  <si>
-    <t>Step2MinRemainRatio</t>
-  </si>
-  <si>
-    <t>Step2距目标最小保留缺口（占Step2_Mon比例，实际钳制在0.001~0.01）</t>
   </si>
   <si>
     <t>EliminationRewardCount</t>
@@ -1242,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1513,7 +1480,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="1">
-        <v>1000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -1524,7 +1491,7 @@
         <v>50</v>
       </c>
       <c r="D25" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -1535,7 +1502,7 @@
         <v>52</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="2:4">
@@ -1545,41 +1512,41 @@
       <c r="C27" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>55</v>
+      <c r="D27" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
       <c r="D28" s="1">
-        <v>300</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
       <c r="D29" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" t="s">
         <v>60</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D30" s="1">
-        <v>30</v>
       </c>
     </row>
     <row r="31" spans="2:4">
@@ -1590,7 +1557,7 @@
         <v>63</v>
       </c>
       <c r="D31" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="2:4">
@@ -1600,73 +1567,18 @@
       <c r="C32" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>66</v>
+      <c r="D32" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
         <v>67</v>
       </c>
-      <c r="C33" t="s">
-        <v>68</v>
-      </c>
       <c r="D33" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="1">
         <v>10</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="17175"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -241,6 +241,12 @@
   </si>
   <si>
     <t>胜利奖励倍数</t>
+  </si>
+  <si>
+    <t>lifeCoin</t>
+  </si>
+  <si>
+    <t>补充1点生命值需要的金币数</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1580,6 +1586,17 @@
       </c>
       <c r="D33" s="1">
         <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="1">
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>补充1点生命值需要的金币数</t>
+  </si>
+  <si>
+    <t>ballsCoin</t>
+  </si>
+  <si>
+    <t>补充5个球需要的金币数</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1596,6 +1602,17 @@
         <v>69</v>
       </c>
       <c r="D34" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="1">
         <v>900</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>补充5个球需要的金币数</t>
+  </si>
+  <si>
+    <t>propCoin</t>
+  </si>
+  <si>
+    <t>补充道具需要的金币数</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1613,6 +1619,17 @@
         <v>71</v>
       </c>
       <c r="D35" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="1">
         <v>900</v>
       </c>
     </row>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1553,7 +1553,7 @@
         <v>58</v>
       </c>
       <c r="D29" s="1">
-        <v>10</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="30" spans="2:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1267,7 +1267,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="81">
   <si>
     <t>#</t>
   </si>
@@ -259,6 +259,27 @@
   </si>
   <si>
     <t>补充道具需要的金币数</t>
+  </si>
+  <si>
+    <t>BonusesPoolTotal</t>
+  </si>
+  <si>
+    <t>奖金池总数</t>
+  </si>
+  <si>
+    <t>BonusesPoolFirst</t>
+  </si>
+  <si>
+    <t>奖金池初始值</t>
+  </si>
+  <si>
+    <t>100,200</t>
+  </si>
+  <si>
+    <t>BonusesPoolAdd</t>
+  </si>
+  <si>
+    <t>奖金池递增值</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1631,6 +1652,39 @@
       </c>
       <c r="D36" s="1">
         <v>900</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1398,7 +1398,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="1">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -1420,7 +1420,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">

--- a/AAAGameData/Configs/GameConfig.xlsx
+++ b/AAAGameData/Configs/GameConfig.xlsx
@@ -273,7 +273,7 @@
     <t>奖金池初始值</t>
   </si>
   <si>
-    <t>100,200</t>
+    <t>1000,2000</t>
   </si>
   <si>
     <t>BonusesPoolAdd</t>
